--- a/artfynd/A 36298-2022 artfynd.xlsx
+++ b/artfynd/A 36298-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119606768</v>
+        <v>119606759</v>
       </c>
       <c r="B2" t="n">
-        <v>91832</v>
+        <v>97824</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,48 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ringstad, Vrm</t>
@@ -799,10 +808,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119606759</v>
+        <v>119606768</v>
       </c>
       <c r="B3" t="n">
-        <v>97824</v>
+        <v>91832</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,48 +820,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ringstad, Vrm</t>

--- a/artfynd/A 36298-2022 artfynd.xlsx
+++ b/artfynd/A 36298-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119606759</v>
+        <v>119606768</v>
       </c>
       <c r="B2" t="n">
-        <v>97824</v>
+        <v>91832</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,48 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ringstad, Vrm</t>
@@ -808,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119606768</v>
+        <v>119606759</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>97824</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,39 +811,48 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ringstad, Vrm</t>
